--- a/public/exports-with-coowners/26696348.xlsx
+++ b/public/exports-with-coowners/26696348.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033111</t>
+          <t xml:space="preserve">200033151</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">

--- a/public/exports-with-coowners/26696348.xlsx
+++ b/public/exports-with-coowners/26696348.xlsx
@@ -10039,7 +10039,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035229</t>
+          <t xml:space="preserve">200035250</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878988</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878984</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">

--- a/public/exports-with-coowners/26696348.xlsx
+++ b/public/exports-with-coowners/26696348.xlsx
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033151</t>
+          <t xml:space="preserve">200033111</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035250</t>
+          <t xml:space="preserve">200035229</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878988</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878984</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
